--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104582_W14.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104582_W14.xlsx
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.6972</v>
+        <v>5.2741</v>
       </c>
       <c r="E2" t="n">
-        <v>7.327</v>
+        <v>6.1945</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.6298</v>
+        <v>-0.9204</v>
       </c>
       <c r="G2" t="n">
-        <v>4.4092</v>
+        <v>4.4063</v>
       </c>
       <c r="H2" t="n">
-        <v>2.2554</v>
+        <v>2.2492</v>
       </c>
       <c r="I2" t="n">
-        <v>2.1538</v>
+        <v>2.1571</v>
       </c>
       <c r="J2" t="n">
-        <v>4.2646</v>
+        <v>4.248</v>
       </c>
       <c r="K2" t="n">
-        <v>2.9958</v>
+        <v>2.982</v>
       </c>
       <c r="L2" t="n">
-        <v>1.2688</v>
+        <v>1.2661</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1446</v>
+        <v>0.1583</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.7403999999999999</v>
+        <v>-0.7328</v>
       </c>
       <c r="O2" t="n">
-        <v>0.885</v>
+        <v>0.8911</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S2" t="n">
-        <v>2.1292</v>
+        <v>0.7085</v>
       </c>
       <c r="T2" t="n">
-        <v>2.0113</v>
+        <v>0.9056999999999999</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1179</v>
+        <v>-0.1972</v>
       </c>
       <c r="V2" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
       <c r="W2" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.7997</v>
+        <v>-1.792</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>G. RADZEVICIUS</t>
+          <t>K. SIMMONS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.0921</v>
+        <v>3.5537</v>
       </c>
       <c r="E3" t="n">
-        <v>3.1023</v>
+        <v>3.272</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.0102</v>
+        <v>0.2817</v>
       </c>
       <c r="G3" t="n">
-        <v>3.676</v>
+        <v>5.3192</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7199</v>
+        <v>-0.8069</v>
       </c>
       <c r="I3" t="n">
-        <v>2.956</v>
+        <v>6.1261</v>
       </c>
       <c r="J3" t="n">
-        <v>4.3363</v>
+        <v>5.2724</v>
       </c>
       <c r="K3" t="n">
-        <v>0.8312</v>
+        <v>-0.6625</v>
       </c>
       <c r="L3" t="n">
-        <v>3.5051</v>
+        <v>5.9349</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.6603</v>
+        <v>0.0468</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.1113</v>
+        <v>-0.1444</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.549</v>
+        <v>0.1912</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.8147</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R3" t="n">
-        <v>0.4537</v>
+        <v>1.3658</v>
       </c>
       <c r="S3" t="n">
-        <v>1.3235</v>
+        <v>0.2345</v>
       </c>
       <c r="T3" t="n">
-        <v>1.0344</v>
+        <v>0.2759</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2891</v>
+        <v>-0.0414</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>K. SIMMONS</t>
+          <t>G. RADZEVICIUS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.633</v>
+        <v>1.433</v>
       </c>
       <c r="E4" t="n">
-        <v>1.8851</v>
+        <v>2.61</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.2521</v>
+        <v>-1.177</v>
       </c>
       <c r="G4" t="n">
-        <v>5.3376</v>
+        <v>3.677</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.8037</v>
+        <v>0.7262999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>6.1413</v>
+        <v>2.9507</v>
       </c>
       <c r="J4" t="n">
-        <v>5.3178</v>
+        <v>4.32</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.6447000000000001</v>
+        <v>0.8274</v>
       </c>
       <c r="L4" t="n">
-        <v>5.9626</v>
+        <v>3.4926</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0197</v>
+        <v>-0.643</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.159</v>
+        <v>-0.1011</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1787</v>
+        <v>-0.5419</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.9073</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R4" t="n">
-        <v>1.361</v>
+        <v>0.4553</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.7046</v>
+        <v>0.6666</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.1644</v>
+        <v>0.5664</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.5402</v>
+        <v>0.1002</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="5">
@@ -799,40 +799,40 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8485</v>
+        <v>0.6284</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.9607</v>
+        <v>-0.9699</v>
       </c>
       <c r="F5" t="n">
-        <v>1.8092</v>
+        <v>1.5983</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1598</v>
+        <v>0.1579</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5439000000000001</v>
+        <v>-0.5483</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7037</v>
+        <v>0.7062</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.9093</v>
+        <v>-0.9188</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.9839</v>
+        <v>-0.9932</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M5" t="n">
-        <v>1.0691</v>
+        <v>1.0766</v>
       </c>
       <c r="N5" t="n">
-        <v>0.44</v>
+        <v>0.4449</v>
       </c>
       <c r="O5" t="n">
-        <v>0.6291</v>
+        <v>0.6317</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -844,13 +844,13 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6887</v>
+        <v>0.4705</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0514</v>
+        <v>-0.0512</v>
       </c>
       <c r="U5" t="n">
-        <v>0.7401</v>
+        <v>0.5217000000000001</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R. KURUCS</t>
+          <t>T. LUWAWU-CABARROT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6683</v>
+        <v>0.5567</v>
       </c>
       <c r="E6" t="n">
-        <v>2.5679</v>
+        <v>0.9649</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.8996</v>
+        <v>-0.4082</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.141</v>
+        <v>-0.097</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.9189</v>
+        <v>-1.9641</v>
       </c>
       <c r="I6" t="n">
-        <v>1.7779</v>
+        <v>1.8671</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9474</v>
+        <v>0.3312</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.4382</v>
+        <v>-0.8144</v>
       </c>
       <c r="L6" t="n">
-        <v>2.3856</v>
+        <v>1.1456</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.0884</v>
+        <v>-0.4282</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.4807</v>
+        <v>-1.1497</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.6077</v>
+        <v>0.7215</v>
       </c>
       <c r="P6" t="n">
-        <v>0.4537</v>
+        <v>1.5934</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S6" t="n">
-        <v>2.5124</v>
+        <v>1.2392</v>
       </c>
       <c r="T6" t="n">
-        <v>2.8188</v>
+        <v>0.6337</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3064</v>
+        <v>0.6055</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.1568</v>
+        <v>-2.1789</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.06419999999999999</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.0927</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>T. LUWAWU-CABARROT</t>
+          <t>M. SPAGNOLO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1925</v>
+        <v>0.3722</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2878</v>
+        <v>0.5955</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.4802</v>
+        <v>-0.2233</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.06950000000000001</v>
+        <v>-0.2874</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.9565</v>
+        <v>-0.6032999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>1.887</v>
+        <v>0.3159</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3875</v>
+        <v>0.6306</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.7904</v>
+        <v>0.6755</v>
       </c>
       <c r="L7" t="n">
-        <v>1.1779</v>
+        <v>-0.0449</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.457</v>
+        <v>-0.918</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.1662</v>
+        <v>-1.2788</v>
       </c>
       <c r="O7" t="n">
-        <v>0.7091</v>
+        <v>0.3608</v>
       </c>
       <c r="P7" t="n">
-        <v>1.5878</v>
+        <v>0.9105</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5878</v>
+        <v>0.9105</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4745</v>
+        <v>0.2938</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0998</v>
+        <v>-0.0351</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5743</v>
+        <v>0.3289</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.1853</v>
+        <v>-0.5447</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.1853</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. SPAGNOLO</t>
+          <t>M. HOWARD</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.3216</v>
+        <v>0.0005</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0195</v>
+        <v>-0.82</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3411</v>
+        <v>0.8205</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.2915</v>
+        <v>-0.362</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.6061</v>
+        <v>-1.112</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3145</v>
+        <v>0.75</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6455</v>
+        <v>-0.2785</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6856</v>
+        <v>-0.307</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.04</v>
+        <v>0.0285</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.9371</v>
+        <v>-0.0835</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.2917</v>
+        <v>-0.805</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3546</v>
+        <v>0.7215</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9073</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3911</v>
+        <v>0.6388</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6261</v>
+        <v>0.6454</v>
       </c>
       <c r="U8" t="n">
-        <v>0.235</v>
+        <v>-0.0066</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.5463</v>
+        <v>1.0895</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.5463</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R. VILLAR</t>
+          <t>S. JOKSIMOVIC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.8091</v>
+        <v>-0.7096</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.8385</v>
+        <v>0.1763</v>
       </c>
       <c r="F9" t="n">
-        <v>1.0293</v>
+        <v>-0.8858</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.5676</v>
+        <v>-1.2937</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1198</v>
+        <v>-0.06619999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4478</v>
+        <v>-1.2275</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.8317</v>
+        <v>0.1694</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.7171</v>
+        <v>0.8101</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.1147</v>
+        <v>-0.6407</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2641</v>
+        <v>-1.4631</v>
       </c>
       <c r="N9" t="n">
-        <v>0.5973000000000001</v>
+        <v>-0.8763</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.3331</v>
+        <v>-0.5868</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.9073</v>
+        <v>0.6829</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.2268</v>
+        <v>0.6829</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5051</v>
+        <v>-0.0988</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0333</v>
+        <v>0.0068</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5383</v>
+        <v>-0.1057</v>
       </c>
       <c r="V9" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>E. OMORUYI</t>
+          <t>R. KURUCS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.1673</v>
+        <v>-0.7607</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1062</v>
+        <v>1.0139</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.0611</v>
+        <v>-1.7747</v>
       </c>
       <c r="G10" t="n">
-        <v>1.67</v>
+        <v>-1.1546</v>
       </c>
       <c r="H10" t="n">
-        <v>0.9956</v>
+        <v>-2.9317</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6744</v>
+        <v>1.7771</v>
       </c>
       <c r="J10" t="n">
-        <v>2.0317</v>
+        <v>0.9094</v>
       </c>
       <c r="K10" t="n">
-        <v>1.4373</v>
+        <v>-1.4661</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5944</v>
+        <v>2.3755</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.3617</v>
+        <v>-2.064</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.4417</v>
+        <v>-1.4656</v>
       </c>
       <c r="O10" t="n">
-        <v>0.08</v>
+        <v>-0.5984</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.722</v>
+        <v>0.4553</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.4025</v>
+        <v>-1.1382</v>
       </c>
       <c r="R10" t="n">
-        <v>0.6805</v>
+        <v>1.5934</v>
       </c>
       <c r="S10" t="n">
-        <v>1.9093</v>
+        <v>1.0995</v>
       </c>
       <c r="T10" t="n">
-        <v>1.1039</v>
+        <v>1.3141</v>
       </c>
       <c r="U10" t="n">
-        <v>0.8054</v>
+        <v>-0.2146</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.0246</v>
+        <v>-1.1609</v>
       </c>
       <c r="W10" t="n">
-        <v>0.1607</v>
+        <v>-0.07140000000000001</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.1853</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S. JOKSIMOVIC</t>
+          <t>R. VILLAR</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.1673</v>
+        <v>-0.8110000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.2406</v>
+        <v>-1.8531</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.9267</v>
+        <v>1.0421</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.294</v>
+        <v>-0.5647</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.0678</v>
+        <v>-0.1179</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.2262</v>
+        <v>-0.4468</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1768</v>
+        <v>-0.8401</v>
       </c>
       <c r="K11" t="n">
-        <v>0.8139</v>
+        <v>-0.7207</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.6371</v>
+        <v>-0.1194</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.4708</v>
+        <v>0.2754</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.8817</v>
+        <v>0.6028</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.5891</v>
+        <v>-0.3275</v>
       </c>
       <c r="P11" t="n">
-        <v>0.6805</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R11" t="n">
-        <v>0.6805</v>
+        <v>0.2276</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5538</v>
+        <v>0.5064</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4174</v>
+        <v>-0.0327</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1364</v>
+        <v>0.5391</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. HOWARD</t>
+          <t>E. OMORUYI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.5476</v>
+        <v>-1.8456</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.0266</v>
+        <v>-0.7203000000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>0.479</v>
+        <v>-1.1254</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.3538</v>
+        <v>1.6772</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.1213</v>
+        <v>0.9993</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7675</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.2431</v>
+        <v>2.0188</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.3015</v>
+        <v>1.4307</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0584</v>
+        <v>0.5881</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.1107</v>
+        <v>-0.3416</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.8198</v>
+        <v>-0.4314</v>
       </c>
       <c r="O12" t="n">
-        <v>0.7091</v>
+        <v>0.0898</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.361</v>
+        <v>-2.7316</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.2683</v>
+        <v>-3.4145</v>
       </c>
       <c r="R12" t="n">
-        <v>0.9073</v>
+        <v>0.6829</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.9255</v>
+        <v>1.2299</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6079</v>
+        <v>0.5177</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3176</v>
+        <v>0.7123</v>
       </c>
       <c r="V12" t="n">
-        <v>1.0927</v>
+        <v>-2.0212</v>
       </c>
       <c r="W12" t="n">
-        <v>1.0927</v>
+        <v>0.1578</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.2137</v>
+        <v>-2.4811</v>
       </c>
       <c r="E13" t="n">
-        <v>0.6015</v>
+        <v>0.5426</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.8152</v>
+        <v>-3.0238</v>
       </c>
       <c r="G13" t="n">
-        <v>1.1667</v>
+        <v>1.1858</v>
       </c>
       <c r="H13" t="n">
-        <v>0.8627</v>
+        <v>0.8726</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3039</v>
+        <v>0.3132</v>
       </c>
       <c r="J13" t="n">
-        <v>2.1651</v>
+        <v>2.1575</v>
       </c>
       <c r="K13" t="n">
-        <v>1.1949</v>
+        <v>1.1893</v>
       </c>
       <c r="L13" t="n">
-        <v>0.9702</v>
+        <v>0.9681999999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.9984</v>
+        <v>-0.9717</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.3321</v>
+        <v>-0.3168</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.6663</v>
+        <v>-0.6549</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R13" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S13" t="n">
-        <v>1.805</v>
+        <v>1.512</v>
       </c>
       <c r="T13" t="n">
-        <v>0.7047</v>
+        <v>0.6614</v>
       </c>
       <c r="U13" t="n">
-        <v>1.1003</v>
+        <v>0.8506</v>
       </c>
       <c r="V13" t="n">
-        <v>-3.8243</v>
+        <v>-3.8132</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-3.8243</v>
+        <v>-3.8132</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.519999999999998</v>
+        <v>5.210599999999998</v>
       </c>
       <c r="E14" t="n">
-        <v>10.6185</v>
+        <v>11.0064</v>
       </c>
       <c r="F14" t="n">
-        <v>-6.0985</v>
+        <v>-5.795999999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>12.7019</v>
+        <v>12.664</v>
       </c>
       <c r="H14" t="n">
-        <v>-3.3044</v>
+        <v>-3.303</v>
       </c>
       <c r="I14" t="n">
-        <v>16.006</v>
+        <v>15.967</v>
       </c>
       <c r="J14" t="n">
-        <v>18.2886</v>
+        <v>18.0199</v>
       </c>
       <c r="K14" t="n">
-        <v>3.0829</v>
+        <v>2.9511</v>
       </c>
       <c r="L14" t="n">
-        <v>15.2058</v>
+        <v>15.069</v>
       </c>
       <c r="M14" t="n">
-        <v>-5.5869</v>
+        <v>-5.356</v>
       </c>
       <c r="N14" t="n">
-        <v>-6.3873</v>
+        <v>-6.2542</v>
       </c>
       <c r="O14" t="n">
-        <v>0.8003999999999999</v>
+        <v>0.8981000000000001</v>
       </c>
       <c r="P14" t="n">
-        <v>-5.6708</v>
+        <v>-5.6908</v>
       </c>
       <c r="Q14" t="n">
-        <v>-15.8783</v>
+        <v>-15.9343</v>
       </c>
       <c r="R14" t="n">
-        <v>10.2073</v>
+        <v>10.2433</v>
       </c>
       <c r="S14" t="n">
-        <v>7.7727</v>
+        <v>8.5009</v>
       </c>
       <c r="T14" t="n">
-        <v>4.6728</v>
+        <v>5.408100000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>3.0998</v>
+        <v>3.0928</v>
       </c>
       <c r="V14" t="n">
-        <v>-10.2837</v>
+        <v>-10.2636</v>
       </c>
       <c r="W14" t="n">
-        <v>3.5352</v>
+        <v>3.5126</v>
       </c>
       <c r="X14" t="n">
-        <v>-13.819</v>
+        <v>-13.7762</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.1141</v>
+        <v>4.2816</v>
       </c>
       <c r="E15" t="n">
-        <v>6.1038</v>
+        <v>5.012</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.9898</v>
+        <v>-0.7304</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.8909</v>
+        <v>-0.8827</v>
       </c>
       <c r="H15" t="n">
-        <v>1.9264</v>
+        <v>1.9217</v>
       </c>
       <c r="I15" t="n">
-        <v>-2.8174</v>
+        <v>-2.8044</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6675</v>
+        <v>0.6441</v>
       </c>
       <c r="K15" t="n">
-        <v>1.2672</v>
+        <v>1.2476</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.5998</v>
+        <v>-0.6035</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.5584</v>
+        <v>-1.5268</v>
       </c>
       <c r="N15" t="n">
-        <v>0.6592</v>
+        <v>0.6741</v>
       </c>
       <c r="O15" t="n">
-        <v>-2.2176</v>
+        <v>-2.2009</v>
       </c>
       <c r="P15" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S15" t="n">
-        <v>0.4606</v>
+        <v>-0.382</v>
       </c>
       <c r="T15" t="n">
-        <v>1.612</v>
+        <v>0.5547</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.1514</v>
+        <v>-0.9367</v>
       </c>
       <c r="V15" t="n">
-        <v>3.5029</v>
+        <v>3.4976</v>
       </c>
       <c r="W15" t="n">
-        <v>3.8243</v>
+        <v>3.8132</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="16">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.5911</v>
+        <v>2.7986</v>
       </c>
       <c r="E16" t="n">
-        <v>3.4654</v>
+        <v>3.5101</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.8743</v>
+        <v>-0.7115</v>
       </c>
       <c r="G16" t="n">
-        <v>1.8322</v>
+        <v>1.8144</v>
       </c>
       <c r="H16" t="n">
-        <v>2.7145</v>
+        <v>2.6978</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.8823</v>
+        <v>-0.8834</v>
       </c>
       <c r="J16" t="n">
-        <v>3.481</v>
+        <v>3.4266</v>
       </c>
       <c r="K16" t="n">
-        <v>2.5589</v>
+        <v>2.5263</v>
       </c>
       <c r="L16" t="n">
-        <v>0.9221</v>
+        <v>0.9002</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.6488</v>
+        <v>-1.6122</v>
       </c>
       <c r="N16" t="n">
-        <v>0.1556</v>
+        <v>0.1715</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.8044</v>
+        <v>-1.7836</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R16" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.9312</v>
+        <v>-0.6908</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1089</v>
+        <v>0.2296</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.0401</v>
+        <v>-0.9204</v>
       </c>
       <c r="V16" t="n">
-        <v>3.278</v>
+        <v>3.2684</v>
       </c>
       <c r="W16" t="n">
-        <v>3.278</v>
+        <v>3.2684</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. BEST</t>
+          <t>K. KURIC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.067</v>
+        <v>1.7194</v>
       </c>
       <c r="E17" t="n">
-        <v>1.8615</v>
+        <v>1.5937</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.7945</v>
+        <v>0.1257</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.336</v>
+        <v>-0.2063</v>
       </c>
       <c r="H17" t="n">
-        <v>1.8844</v>
+        <v>-1.0049</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.2204</v>
+        <v>0.7986</v>
       </c>
       <c r="J17" t="n">
-        <v>2.2296</v>
+        <v>1.0088</v>
       </c>
       <c r="K17" t="n">
-        <v>2.3897</v>
+        <v>-0.6592</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.1601</v>
+        <v>1.668</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.5656</v>
+        <v>-1.215</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.5053</v>
+        <v>-0.3457</v>
       </c>
       <c r="O17" t="n">
-        <v>-2.0603</v>
+        <v>-0.8694</v>
       </c>
       <c r="P17" t="n">
-        <v>1.361</v>
+        <v>1.8211</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.4952</v>
+        <v>1.8211</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.0507</v>
+        <v>-0.9849</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3266</v>
+        <v>-0.5044999999999999</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.7241</v>
+        <v>-0.4804</v>
       </c>
       <c r="V17" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W17" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R. GUERRERO</t>
+          <t>A. BEST</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.712</v>
+        <v>1.2326</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1717</v>
+        <v>1.7063</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8837</v>
+        <v>-0.4737</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.1729</v>
+        <v>-0.3331</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.3089</v>
+        <v>1.8895</v>
       </c>
       <c r="I18" t="n">
-        <v>0.136</v>
+        <v>-2.2226</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1066</v>
+        <v>2.1991</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0693</v>
+        <v>2.3787</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0373</v>
+        <v>-0.1796</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.2795</v>
+        <v>-2.5321</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.3781</v>
+        <v>-0.4891</v>
       </c>
       <c r="O18" t="n">
-        <v>0.09859999999999999</v>
+        <v>-2.043</v>
       </c>
       <c r="P18" t="n">
-        <v>0.6805</v>
+        <v>1.3658</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R18" t="n">
-        <v>0.6805</v>
+        <v>2.5039</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2044</v>
+        <v>-0.8895999999999999</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2782</v>
+        <v>-0.4441</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4827</v>
+        <v>-0.4455</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>K. KURIC</t>
+          <t>R. GUERRERO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5044999999999999</v>
+        <v>0.5332</v>
       </c>
       <c r="E19" t="n">
-        <v>1.0399</v>
+        <v>-0.1726</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.5354</v>
+        <v>0.7058</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.2041</v>
+        <v>-0.166</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.9984</v>
+        <v>-0.3047</v>
       </c>
       <c r="I19" t="n">
-        <v>0.7944</v>
+        <v>0.1387</v>
       </c>
       <c r="J19" t="n">
-        <v>1.042</v>
+        <v>0.1062</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.6345</v>
+        <v>0.0689</v>
       </c>
       <c r="L19" t="n">
-        <v>1.6765</v>
+        <v>0.0372</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.2461</v>
+        <v>-0.2722</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.3639</v>
+        <v>-0.3736</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.8822</v>
+        <v>0.1014</v>
       </c>
       <c r="P19" t="n">
-        <v>1.8147</v>
+        <v>0.6829</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.8147</v>
+        <v>0.6829</v>
       </c>
       <c r="S19" t="n">
-        <v>-2.1988</v>
+        <v>0.0163</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.0948</v>
+        <v>-0.2788</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.1039</v>
+        <v>0.2951</v>
       </c>
       <c r="V19" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.4589</v>
+        <v>-0.5915</v>
       </c>
       <c r="E20" t="n">
-        <v>1.4221</v>
+        <v>1.5218</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.881</v>
+        <v>-2.1133</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.0554</v>
+        <v>-1.0466</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1067</v>
+        <v>0.109</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.1621</v>
+        <v>-1.1557</v>
       </c>
       <c r="J20" t="n">
-        <v>0.9058</v>
+        <v>0.9018</v>
       </c>
       <c r="K20" t="n">
-        <v>0.8312</v>
+        <v>0.8274</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.9612</v>
+        <v>-1.9485</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.7245</v>
+        <v>-0.7184</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.2368</v>
+        <v>-1.2301</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R20" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0236</v>
+        <v>-0.1092</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6956</v>
+        <v>-0.5786</v>
       </c>
       <c r="U20" t="n">
-        <v>0.7192</v>
+        <v>0.4694</v>
       </c>
       <c r="V20" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="W20" t="n">
-        <v>2.3461</v>
+        <v>2.3367</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="21">
@@ -2047,58 +2047,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.9977</v>
+        <v>-0.6337</v>
       </c>
       <c r="E21" t="n">
-        <v>0.7611</v>
+        <v>0.6288</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.7587</v>
+        <v>-1.2624</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.544</v>
+        <v>-0.5315</v>
       </c>
       <c r="H21" t="n">
-        <v>2.0735</v>
+        <v>2.0764</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.6175</v>
+        <v>-2.6079</v>
       </c>
       <c r="J21" t="n">
-        <v>1.369</v>
+        <v>1.356</v>
       </c>
       <c r="K21" t="n">
-        <v>2.0434</v>
+        <v>2.0339</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6744</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.913</v>
+        <v>-1.8876</v>
       </c>
       <c r="N21" t="n">
-        <v>0.0301</v>
+        <v>0.0424</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.9431</v>
+        <v>-1.93</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4537</v>
+        <v>-0.1021</v>
       </c>
       <c r="T21" t="n">
-        <v>0.5263</v>
+        <v>0.4109</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.9799</v>
+        <v>-0.513</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.3846</v>
+        <v>-1.2416</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.5582</v>
+        <v>-0.2335</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.8264</v>
+        <v>-1.0081</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.9739</v>
+        <v>-0.9651999999999999</v>
       </c>
       <c r="H22" t="n">
-        <v>0.6175</v>
+        <v>0.6257</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.5913</v>
+        <v>-1.5909</v>
       </c>
       <c r="J22" t="n">
-        <v>0.9441000000000001</v>
+        <v>0.9236</v>
       </c>
       <c r="K22" t="n">
-        <v>1.4373</v>
+        <v>1.4307</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.4932</v>
+        <v>-0.5071</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.9179</v>
+        <v>-1.8888</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.8198</v>
+        <v>-0.805</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.0981</v>
+        <v>-1.0838</v>
       </c>
       <c r="P22" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R22" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.3181</v>
+        <v>-1.1869</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.4608</v>
+        <v>-1.1084</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1427</v>
+        <v>-0.0785</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="23">
@@ -2203,58 +2203,58 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.5389</v>
+        <v>-1.3136</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.1767</v>
+        <v>-2.0669</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6378</v>
+        <v>0.7533</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.2291</v>
+        <v>-2.2195</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.1256</v>
+        <v>-1.1204</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.1035</v>
+        <v>-1.0991</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.4115</v>
+        <v>-1.4186</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.6998</v>
+        <v>-0.7035</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.7117</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.8176</v>
+        <v>-0.8008999999999999</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.4258</v>
+        <v>-0.4169</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.3918</v>
+        <v>-0.384</v>
       </c>
       <c r="P23" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6708</v>
+        <v>-0.4599</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7652</v>
+        <v>-0.6483</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0944</v>
+        <v>0.1884</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.6561</v>
+        <v>-4.7905</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.2689</v>
+        <v>-1.4042</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.3873</v>
+        <v>-3.3863</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.8238</v>
+        <v>-2.8119</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.0491</v>
+        <v>-0.0461</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.7747</v>
+        <v>-2.7658</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.4523</v>
+        <v>-0.4679</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.111</v>
+        <v>-0.1174</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.3413</v>
+        <v>-0.3505</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.3716</v>
+        <v>-2.3441</v>
       </c>
       <c r="N24" t="n">
-        <v>0.0619</v>
+        <v>0.0713</v>
       </c>
       <c r="O24" t="n">
-        <v>-2.4335</v>
+        <v>-2.4154</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R24" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.5108</v>
+        <v>-0.663</v>
       </c>
       <c r="T24" t="n">
-        <v>0.3176</v>
+        <v>0.2018</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.8284</v>
+        <v>-0.8648</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.8678</v>
+        <v>-0.8603</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.8678</v>
+        <v>-0.8603</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.4725</v>
+        <v>-4.9286</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.3799</v>
+        <v>-4.2995</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.0926</v>
+        <v>-0.6291</v>
       </c>
       <c r="G25" t="n">
-        <v>-5.3039</v>
+        <v>-5.3155</v>
       </c>
       <c r="H25" t="n">
-        <v>-3.5366</v>
+        <v>-3.541</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.7673</v>
+        <v>-1.7744</v>
       </c>
       <c r="J25" t="n">
-        <v>-3.295</v>
+        <v>-3.3237</v>
       </c>
       <c r="K25" t="n">
-        <v>-2.7645</v>
+        <v>-2.7794</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.5306</v>
+        <v>-0.5443</v>
       </c>
       <c r="M25" t="n">
-        <v>-2.0089</v>
+        <v>-1.9918</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.7721</v>
+        <v>-0.7617</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.2368</v>
+        <v>-1.2301</v>
       </c>
       <c r="P25" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R25" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.3274</v>
+        <v>-0.7725</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.0434</v>
+        <v>-0.9271</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.284</v>
+        <v>0.1546</v>
       </c>
       <c r="V25" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.9317</v>
       </c>
       <c r="W25" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-4.520000000000001</v>
+        <v>-2.934100000000001</v>
       </c>
       <c r="E26" t="n">
-        <v>6.098399999999997</v>
+        <v>5.795999999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>-10.6185</v>
+        <v>-8.729999999999999</v>
       </c>
       <c r="G26" t="n">
-        <v>-12.7018</v>
+        <v>-12.6639</v>
       </c>
       <c r="H26" t="n">
-        <v>3.3044</v>
+        <v>3.303</v>
       </c>
       <c r="I26" t="n">
-        <v>-16.0061</v>
+        <v>-15.9669</v>
       </c>
       <c r="J26" t="n">
-        <v>5.5868</v>
+        <v>5.356000000000002</v>
       </c>
       <c r="K26" t="n">
-        <v>6.3872</v>
+        <v>6.254</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.8005999999999998</v>
+        <v>-0.8982000000000001</v>
       </c>
       <c r="M26" t="n">
-        <v>-18.2886</v>
+        <v>-18.02</v>
       </c>
       <c r="N26" t="n">
-        <v>-3.0827</v>
+        <v>-2.9511</v>
       </c>
       <c r="O26" t="n">
-        <v>-15.206</v>
+        <v>-15.0689</v>
       </c>
       <c r="P26" t="n">
-        <v>5.670799999999999</v>
+        <v>5.690799999999999</v>
       </c>
       <c r="Q26" t="n">
-        <v>-10.2077</v>
+        <v>-10.2437</v>
       </c>
       <c r="R26" t="n">
-        <v>15.8785</v>
+        <v>15.9344</v>
       </c>
       <c r="S26" t="n">
-        <v>-7.772899999999999</v>
+        <v>-6.224600000000001</v>
       </c>
       <c r="T26" t="n">
-        <v>-3.0998</v>
+        <v>-3.0928</v>
       </c>
       <c r="U26" t="n">
-        <v>-4.672800000000001</v>
+        <v>-3.1318</v>
       </c>
       <c r="V26" t="n">
-        <v>10.2839</v>
+        <v>10.2636</v>
       </c>
       <c r="W26" t="n">
-        <v>13.8192</v>
+        <v>13.7763</v>
       </c>
       <c r="X26" t="n">
-        <v>-3.5353</v>
+        <v>-3.5126</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104582_W14.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104582_W14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-1.792</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104582_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104582_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104582_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104582_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104582_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104582_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104582_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104582_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104582_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>0</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104582_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104582_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>-3.8132</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104582_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-13.7762</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104582_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104582_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104582_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104582_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104582_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104582_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104582_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104582_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>0</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104582_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-0.8603</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104582_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104582_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,7 @@
       <c r="X26" t="n">
         <v>-3.5126</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
